--- a/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icesit.sharepoint.com/sites/ExpertGroup/WGRDBES-StockCoord/2026 Meeting Documents/04. Working documents/SCF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC04E036-C640-420E-BD7B-E3BC277F8EE2}"/>
+  <xr:revisionPtr revIDLastSave="464" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5645CF2-89CF-4864-B06F-26CF3D8C3F7B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="SCF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <author>tc={60AF2FFC-B021-42C7-AF40-A1560673A0CC}</author>
   </authors>
   <commentList>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
     //vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="1" shapeId="0" xr:uid="{60AF2FFC-B021-42C7-AF40-A1560673A0CC}">
+    <comment ref="J19" authorId="1" shapeId="0" xr:uid="{60AF2FFC-B021-42C7-AF40-A1560673A0CC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,7 +75,7 @@
     <author>tc={E759D9ED-5F4D-44F2-AB83-3393915E37B6}</author>
   </authors>
   <commentList>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -83,7 +83,7 @@
     //vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</t>
       </text>
     </comment>
-    <comment ref="J25" authorId="1" shapeId="0" xr:uid="{04664D76-2F7C-44B0-ACC2-110B494715CD}">
+    <comment ref="J26" authorId="1" shapeId="0" xr:uid="{04664D76-2F7C-44B0-ACC2-110B494715CD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +92,7 @@
 Further, we need to explore what the stock assessor needs</t>
       </text>
     </comment>
-    <comment ref="J26" authorId="2" shapeId="0" xr:uid="{E759D9ED-5F4D-44F2-AB83-3393915E37B6}">
+    <comment ref="J27" authorId="2" shapeId="0" xr:uid="{E759D9ED-5F4D-44F2-AB83-3393915E37B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="156">
   <si>
     <t>Version</t>
   </si>
@@ -240,9 +240,6 @@
   </si>
   <si>
     <t>Code list</t>
-  </si>
-  <si>
-    <t>Calendar, Model</t>
   </si>
   <si>
     <r>
@@ -473,9 +470,6 @@
     <t>DC</t>
   </si>
   <si>
-    <t>Code list missing</t>
-  </si>
-  <si>
     <t>The class of the distributionType, e.g. if distributionType = LengthTotal then the length classes represented in the estimated length distribution</t>
   </si>
   <si>
@@ -552,10 +546,6 @@
     <t>Count of measurements for the given distributionClass and variableType. It represents the actual number of observations (e.g. individuals measured for age, length, weight, etc.) used to calculate the reported total or mean.  If no measurements were collected for a given distributionClass and variableType , a value of 0 should be reported.  The number may differ per variableType, as not all variables are necessarily measured for the same individuals.</t>
   </si>
   <si>
-    <t>Indicate if year, seasonType and seasonValue align with a calendar year or follow a shifted cycle (model year) that spans across calendar years.
-For most stocks the temporal type is calendar. For a minority of stocks the time is shifted relative to a calendar during stock coordination, this can be indicated by setting temporal type to model</t>
-  </si>
-  <si>
     <t>ICESArea
 //vocab.ices.dk/?ref=358
 AreaNonFAO
@@ -574,10 +564,6 @@
   </si>
   <si>
     <t>timeReferenceType</t>
-  </si>
-  <si>
-    <t>Indicate if year, seasonType and seasonValue align with a calendar year or follow a shifted cycle (model year) that spans across calendar years.
-For most stocks the temporal type is calendar. For a minority of stocks the time is shifted relative to a calendar during stock coordination, this can be indicated by setting time reference type to 'model'</t>
   </si>
   <si>
     <t>Depending on timeReferenceType this is either a calendar year or model year</t>
@@ -696,116 +682,6 @@
   </si>
   <si>
     <t>CC +DC</t>
-  </si>
-  <si>
-    <r>
-      <t>For a minority of stocks, the time is shifted relative to the calendar year, so it better reflects on life cycle of the stock. This process involves moving the birthday from the 1</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>st</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of January to another date and thereby changing the age. E.g., for spr.27.3a4 the birthday is moved from the 1</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>st</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of January to the 1</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>st</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of July, so a model year goes from 3</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>rd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> quarter one year until the end of 2</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t>nd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> the next year. This moving involves changing the ages, so the new birthdays is considered. Since this reassigning of ages to a new birthday is done during stock coordination, then ages won’t match with the calendar year in the output from the stock coordination, so therefor the estimates should not be by calendar year and season, but model year and season</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-timeReferenceType is not part of the unique key (UK), so values can only be reported for either Model or Canlendar, not both.</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Only accept a fixed value CC
@@ -850,12 +726,6 @@
     <t>If needed the assessement input can be split by  fisheries management unit or ICES Area</t>
   </si>
   <si>
-    <t>The value of the specified seasonType.
-If seasonType is Month, then seasonValue must be 1-12.
-If seasonType is Quarter, then seasonValue must be 1-4. 
-Only a single value is accepted</t>
-  </si>
-  <si>
     <t xml:space="preserve">The value of the specified seasonType.
 If seasonType is Month, then seasonValue must be 1-12.
 If seasonType is Quarter, then seasonValue must be 1-4. 
@@ -873,12 +743,57 @@
 Find the CC totalSumConverted for each combination of timeReferenceType, year, workingGroup, stock, catchCategory, seasonType, seasonValue, areaType, areaValue and fleetValue and convert the total to kg by checking if variableUnit= ‘t’ then totalConverted = total*1000 else totalConverted = total (unit is kg like for WeightConverted - everything is in kg). 
 For each DistributionType check If CC totalSumConverted &gt; 1.2*SOP or CC totalSumConverted &lt; 0.8*SOP, if so make an error in the line for CC fields: timeReferenceType, year, workingGroup, stock, catchCategory, seasonType, seasonValue, areaType, areaValue and fleetValue for the field total. Error message: total is &gt; 120 % SOP or total is &lt; 80 % SOP for DistributionType (e.g. age or length) .</t>
   </si>
+  <si>
+    <t>calendarYear</t>
+  </si>
+  <si>
+    <t>Y, N</t>
+  </si>
+  <si>
+    <t>YesNoFields</t>
+  </si>
+  <si>
+    <t>Indicate if year, seasonType and seasonValue align with a calendar year (Y) or follow a shifted cycle (model year) that spans across calendar years (N).
+For most stocks this will be Y. For a minority of stocks the time is shifted relative to a calendar during stock coordination, this can be indicated by setting calendar year to N</t>
+  </si>
+  <si>
+    <t>yearStartDate</t>
+  </si>
+  <si>
+    <t>DD/MM</t>
+  </si>
+  <si>
+    <t>M/O</t>
+  </si>
+  <si>
+    <t>If the year is shifted relative to a calendar during stock coordination, calendarYear = N, the indicate when the year start with month and day, MM-DD, e.g., 07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory if calendarYear = N
+yearStartDate should equal for all rows associated with a stock
+</t>
+  </si>
+  <si>
+    <t>Mandatory if calendarYear = N
+yearStartDate should equal for all rows associated with a stock</t>
+  </si>
+  <si>
+    <t>The value of the specified seasonType.
+If seasonType is Month, then seasonValue must be 1-12.
+If seasonType is Quarter, then seasonValue must be 1-4. 
+If seasonType is HalfYear, then seasonValue must be 1-2. 
+Only a single value is accepted</t>
+  </si>
+  <si>
+    <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. If seasonType = HalfYear, then seasonValue must be 1-2. 
+Only a single value should be accepted in seasonValue</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -988,14 +903,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1011,6 +920,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1043,7 +958,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1101,9 +1016,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1126,18 +1038,26 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1480,10 +1400,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I11" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}">
+  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}">
     <text>//vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</text>
   </threadedComment>
-  <threadedComment ref="J18" dT="2026-06-10T06:44:30.23" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{60AF2FFC-B021-42C7-AF40-A1560673A0CC}">
+  <threadedComment ref="J19" dT="2026-06-10T06:44:30.23" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{60AF2FFC-B021-42C7-AF40-A1560673A0CC}">
     <text>Update, when we have a good solution on how to count</text>
   </threadedComment>
 </ThreadedComments>
@@ -1491,14 +1411,14 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I11" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
+  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
     <text>//vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</text>
   </threadedComment>
-  <threadedComment ref="J25" dT="2026-06-10T06:36:31.15" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{04664D76-2F7C-44B0-ACC2-110B494715CD}">
+  <threadedComment ref="J26" dT="2026-06-10T06:36:31.15" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{04664D76-2F7C-44B0-ACC2-110B494715CD}">
     <text>General issues with counts, see gitHub. 
 Further, we need to explore what the stock assessor needs</text>
   </threadedComment>
-  <threadedComment ref="J26" dT="2026-05-09T10:42:55.70" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{E759D9ED-5F4D-44F2-AB83-3393915E37B6}">
+  <threadedComment ref="J27" dT="2026-05-09T10:42:55.70" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{E759D9ED-5F4D-44F2-AB83-3393915E37B6}">
     <text>Updated, when the text for the CC is approved</text>
   </threadedComment>
 </ThreadedComments>
@@ -1529,464 +1449,464 @@
         <v>2</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="26"/>
+      <c r="F2" s="25"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="26"/>
+      <c r="F3" s="25"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="30"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="29"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="28"/>
-      <c r="C5" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="30"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="28"/>
-      <c r="C7" s="29" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="29" t="s">
+      <c r="D7" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="28"/>
+      <c r="G7" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="27"/>
       <c r="I7" s="7"/>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="28"/>
-      <c r="C8" s="28" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28" t="s">
+      <c r="D8" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="31"/>
+      <c r="G8" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="30"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="28"/>
-      <c r="C9" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="31"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="30"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="28"/>
-      <c r="C10" s="28" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28" t="s">
+      <c r="D10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="31"/>
+      <c r="G10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="30"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="28"/>
-      <c r="C11" s="28" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28" t="s">
+      <c r="D11" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="31"/>
+      <c r="G11" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="30"/>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="28"/>
-      <c r="C12" s="28" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28" t="s">
+      <c r="D12" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="31"/>
+      <c r="G12" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="30"/>
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="28"/>
-      <c r="C13" s="28" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28" t="s">
+      <c r="D13" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="31"/>
+      <c r="G13" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="30"/>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="28"/>
-      <c r="C14" s="28" t="s">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28" t="s">
+      <c r="D14" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="31"/>
+      <c r="G14" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="30"/>
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="28"/>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28" t="s">
+      <c r="D15" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="31"/>
+      <c r="G15" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="30"/>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="28"/>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28" t="s">
+      <c r="D16" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="31"/>
+      <c r="G16" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="30"/>
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
-      <c r="C17" s="28" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28" t="s">
+      <c r="D17" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="31"/>
+      <c r="G17" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="30"/>
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="28"/>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28" t="s">
+      <c r="D18" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="31"/>
+      <c r="G18" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="28"/>
-      <c r="C19" s="28" t="s">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28" t="s">
+      <c r="D19" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="28"/>
+      <c r="G19" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="28"/>
-      <c r="C20" s="28" t="s">
+      <c r="B20" s="27"/>
+      <c r="C20" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28" t="s">
+      <c r="D20" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="28"/>
+      <c r="G20" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="28"/>
-      <c r="C21" s="28" t="s">
+      <c r="B21" s="27"/>
+      <c r="C21" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28" t="s">
+      <c r="D21" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="28"/>
+      <c r="G21" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="27"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="28"/>
-      <c r="C22" s="28" t="s">
+      <c r="B22" s="27"/>
+      <c r="C22" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28" t="s">
+      <c r="D22" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="28"/>
+      <c r="G22" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="27"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="28"/>
-      <c r="C23" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="28"/>
+      <c r="G23" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="27"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28" t="s">
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="28"/>
+      <c r="G24" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="27"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="28"/>
+      <c r="G25" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="27"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="28"/>
+      <c r="G26" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="27"/>
       <c r="J26" s="3"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28" t="s">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="28"/>
+      <c r="G27" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="27"/>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="28" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="28"/>
+      <c r="G28" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="27"/>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="28" t="s">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="33"/>
+      <c r="G29" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="32"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="28"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H31" s="28"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
     </row>
     <row r="33" spans="4:8" x14ac:dyDescent="0.3">
       <c r="H33" s="5"/>
@@ -2024,7 +1944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" style="9" customWidth="1"/>
@@ -2054,7 +1974,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>26</v>
@@ -2112,16 +2032,17 @@
         <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:13" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
+        <v>144</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>43</v>
@@ -2132,51 +2053,46 @@
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>86</v>
+      <c r="G4" s="40" t="s">
+        <v>146</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="L4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="5" spans="1:13" s="34" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>117</v>
-      </c>
+      <c r="C5" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="36"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="L5" s="39"/>
     </row>
     <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2186,10 +2102,10 @@
         <v>42</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>2</v>
@@ -2198,16 +2114,16 @@
         <v>44</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2218,7 +2134,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>38</v>
@@ -2230,19 +2146,19 @@
         <v>44</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>41</v>
       </c>
@@ -2250,10 +2166,10 @@
         <v>42</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>2</v>
@@ -2262,16 +2178,16 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -2282,31 +2198,31 @@
         <v>42</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>125</v>
+        <v>56</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
@@ -2314,10 +2230,10 @@
         <v>42</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>4</v>
@@ -2325,23 +2241,20 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>49</v>
+      <c r="G10" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>41</v>
       </c>
@@ -2349,10 +2262,10 @@
         <v>42</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>4</v>
@@ -2361,19 +2274,22 @@
         <v>44</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>41</v>
       </c>
@@ -2381,7 +2297,7 @@
         <v>42</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>38</v>
@@ -2393,25 +2309,19 @@
         <v>44</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>49</v>
+        <v>115</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>114</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
@@ -2419,7 +2329,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>38</v>
@@ -2430,52 +2340,64 @@
       <c r="F13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="10"/>
+      <c r="G13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="J13" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>70</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="C15" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>38</v>
@@ -2487,73 +2409,99 @@
         <v>44</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="I16" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="J16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="K16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="10" t="s">
+    </row>
+    <row r="17" spans="3:11" ht="388.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="388.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="E17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="J17" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="K17" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K16" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J17" s="10" t="s">
+    </row>
+    <row r="19" spans="3:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="C19" s="8" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="3:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="C18" s="8" t="s">
+      <c r="D19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>121</v>
+      <c r="J19" s="23" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2565,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" style="9" customWidth="1"/>
@@ -2582,7 +2530,7 @@
     <col min="13" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
@@ -2590,9 +2538,9 @@
       <c r="I1" s="10"/>
       <c r="L1" s="10"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>26</v>
@@ -2610,7 +2558,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>32</v>
@@ -2628,7 +2576,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B3" s="14"/>
       <c r="C3" s="8" t="s">
         <v>37</v>
@@ -2640,26 +2588,24 @@
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="166.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>115</v>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
+        <v>144</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>43</v>
@@ -2670,53 +2616,48 @@
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="24" t="s">
-        <v>86</v>
+      <c r="G4" s="40" t="s">
+        <v>146</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="L4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="5" spans="1:12" s="34" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C5" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="36"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="L5" s="39"/>
+    </row>
+    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>41</v>
       </c>
@@ -2724,10 +2665,10 @@
         <v>42</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>2</v>
@@ -2736,19 +2677,19 @@
         <v>44</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>41</v>
       </c>
@@ -2756,7 +2697,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>38</v>
@@ -2767,20 +2708,20 @@
       <c r="F7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>53</v>
+      <c r="G7" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>41</v>
       </c>
@@ -2788,10 +2729,10 @@
         <v>42</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>2</v>
@@ -2800,19 +2741,19 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>41</v>
       </c>
@@ -2820,33 +2761,31 @@
         <v>42</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>125</v>
+        <v>56</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" s="37"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
@@ -2854,10 +2793,10 @@
         <v>42</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>4</v>
@@ -2865,24 +2804,21 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>49</v>
+      <c r="G10" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>41</v>
       </c>
@@ -2890,10 +2826,10 @@
         <v>42</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>4</v>
@@ -2902,19 +2838,23 @@
         <v>44</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>118</v>
+        <v>60</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>41</v>
       </c>
@@ -2922,7 +2862,7 @@
         <v>42</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>38</v>
@@ -2934,25 +2874,19 @@
         <v>44</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>49</v>
+        <v>115</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>114</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
@@ -2960,7 +2894,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>38</v>
@@ -2971,54 +2905,65 @@
       <c r="F13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="10"/>
+      <c r="G13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="J13" s="10" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="B14" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>112</v>
-      </c>
+      <c r="G14" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>129</v>
+        <v>119</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="L14" s="10"/>
     </row>
-    <row r="15" spans="1:15" ht="106.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="C15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>38</v>
@@ -3026,109 +2971,103 @@
       <c r="E15" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19"/>
-      <c r="B16" s="9" t="s">
+      <c r="I16" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-    </row>
-    <row r="17" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="C17" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="L17" s="10"/>
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
       <c r="O17" s="19"/>
     </row>
-    <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
-        <v>42</v>
-      </c>
+    <row r="18" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
       <c r="C18" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="J18" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+    </row>
+    <row r="19" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>38</v>
@@ -3139,59 +3078,62 @@
       <c r="F19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="20" t="s">
-        <v>94</v>
+      <c r="G19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L19" s="10"/>
     </row>
-    <row r="20" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>38</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>97</v>
+      <c r="G20" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="L20" s="10"/>
     </row>
-    <row r="21" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="C21" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>38</v>
@@ -3203,25 +3145,25 @@
         <v>44</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="I21" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="L21" s="10"/>
     </row>
-    <row r="22" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C22" s="8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>38</v>
@@ -3233,105 +3175,129 @@
         <v>44</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="K23" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="C24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="J24" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="J25" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:15" ht="72" x14ac:dyDescent="0.3">
-      <c r="C23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="19"/>
-      <c r="J23" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C24" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="J24" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:15" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="36" t="s">
-        <v>121</v>
       </c>
       <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="C26" s="8" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="36" t="s">
-        <v>109</v>
+      <c r="E26" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>117</v>
       </c>
       <c r="L26" s="10"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="C27" s="3"/>
-      <c r="F27" s="9"/>
+    <row r="27" spans="1:15" ht="72" x14ac:dyDescent="0.3">
+      <c r="C27" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>107</v>
+      </c>
       <c r="L27" s="10"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C28" s="3"/>
       <c r="F28" s="9"/>
       <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C29" s="3"/>
+      <c r="F29" s="9"/>
+      <c r="L29" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3347,18 +3313,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>115</v>
+      <c r="A2" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3381,7 +3347,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3408,10 +3374,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3420,15 +3386,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9daeb8933c56b40f3271bb867fbbc8d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a657112-7d30-43e0-84e9-071e428c6b63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d201b2d4740b92ddb00486e196a42d19" ns2:_="">
     <xsd:import namespace="9a657112-7d30-43e0-84e9-071e428c6b63"/>
@@ -3572,6 +3529,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3579,14 +3545,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA6BFD8-8F41-452A-AD77-0631547D8597}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3600,6 +3558,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="464" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5645CF2-89CF-4864-B06F-26CF3D8C3F7B}"/>
+  <xr:revisionPtr revIDLastSave="466" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1ADC4FF-A122-41FA-B4CA-99E206C75FB9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
   </bookViews>
@@ -760,9 +760,6 @@
     <t>yearStartDate</t>
   </si>
   <si>
-    <t>DD/MM</t>
-  </si>
-  <si>
     <t>M/O</t>
   </si>
   <si>
@@ -787,6 +784,9 @@
   <si>
     <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. If seasonType = HalfYear, then seasonValue must be 1-2. 
 Only a single value should be accepted in seasonValue</t>
+  </si>
+  <si>
+    <t>MM-DD</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:13" ht="165.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
@@ -2078,19 +2078,19 @@
         <v>38</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G5" s="36"/>
       <c r="H5" s="39"/>
       <c r="I5" s="37"/>
       <c r="J5" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>151</v>
-      </c>
-      <c r="K5" s="39" t="s">
-        <v>152</v>
       </c>
       <c r="L5" s="39"/>
     </row>
@@ -2283,10 +2283,10 @@
         <v>48</v>
       </c>
       <c r="J11" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="39" t="s">
         <v>154</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2641,19 +2641,19 @@
         <v>38</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G5" s="36"/>
       <c r="H5" s="39"/>
       <c r="I5" s="37"/>
       <c r="J5" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L5" s="39"/>
     </row>
@@ -3386,6 +3386,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9daeb8933c56b40f3271bb867fbbc8d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a657112-7d30-43e0-84e9-071e428c6b63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d201b2d4740b92ddb00486e196a42d19" ns2:_="">
     <xsd:import namespace="9a657112-7d30-43e0-84e9-071e428c6b63"/>
@@ -3529,22 +3544,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA6BFD8-8F41-452A-AD77-0631547D8597}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3562,30 +3586,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" enabled="0" method="" siteId="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" removed="1"/>

--- a/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1ADC4FF-A122-41FA-B4CA-99E206C75FB9}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E6E2786-36F5-4AA6-91F2-5F53FA90FF38}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="SCF" sheetId="1" r:id="rId1"/>
@@ -70,12 +70,12 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={56891298-F473-4CBE-ABBB-E1CEF089D4F3}</author>
+    <author>tc={23CC9277-FDAF-43EE-8833-E4C0F8790F2B}</author>
     <author>tc={04664D76-2F7C-44B0-ACC2-110B494715CD}</author>
     <author>tc={E759D9ED-5F4D-44F2-AB83-3393915E37B6}</author>
   </authors>
   <commentList>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{23CC9277-FDAF-43EE-8833-E4C0F8790F2B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="153">
   <si>
     <t>Version</t>
   </si>
@@ -394,10 +394,6 @@
 //vocab.ices.dk/?ref=1646</t>
   </si>
   <si>
-    <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. 
-Only a single value should be accepted in seasonValue</t>
-  </si>
-  <si>
     <t>//vocab.ices.dk/?ref=1446</t>
   </si>
   <si>
@@ -569,36 +565,6 @@
     <t>Depending on timeReferenceType this is either a calendar year or model year</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ICESArea, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AreaNonFAO</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AreaType - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>code missing for fisheriesManagementUnit (AreaNonFAO)</t>
-    </r>
-  </si>
-  <si>
     <t>The value of the specified areaType.
 Only a single value is accepted</t>
   </si>
@@ -607,40 +573,7 @@
 If the 'total' is based on census data, e.g., landings, then this should be left blank. If the 'total' is estimated, e.g., discard, then this can be filled.</t>
   </si>
   <si>
-    <t>If needed the assessement input can be split by area,  fisheries management unit or ICES Area</t>
-  </si>
-  <si>
     <t>If needed the assessement input can be split by fleet</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TimeUnit - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>code missing for half year</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Quarter, Month, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>halfYear</t>
-    </r>
   </si>
   <si>
     <t>The catch category.
@@ -716,21 +649,8 @@
     <t>FK to DC</t>
   </si>
   <si>
-    <t>Only a single value should be accepted in areaValue</t>
-  </si>
-  <si>
     <t>The temporal aggregation period. Depending on timeReferenceType this is either a calendar time span or model time span.
 If needed the assessement input can be split by quarter,  month or half year</t>
-  </si>
-  <si>
-    <t>If needed the assessement input can be split by  fisheries management unit or ICES Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The value of the specified seasonType.
-If seasonType is Month, then seasonValue must be 1-12.
-If seasonType is Quarter, then seasonValue must be 1-4. 
-Only a single value is accepted
-</t>
   </si>
   <si>
     <t>SOP Calculation.
@@ -775,18 +695,37 @@
 yearStartDate should equal for all rows associated with a stock</t>
   </si>
   <si>
+    <t>MM-DD</t>
+  </si>
+  <si>
+    <t>Quarter, Month, Half-year</t>
+  </si>
+  <si>
+    <t>TimeUnit</t>
+  </si>
+  <si>
     <t>The value of the specified seasonType.
 If seasonType is Month, then seasonValue must be 1-12.
 If seasonType is Quarter, then seasonValue must be 1-4. 
-If seasonType is HalfYear, then seasonValue must be 1-2. 
+If seasonType is Half-year, then seasonValue must be 1-2. 
 Only a single value is accepted</t>
   </si>
   <si>
-    <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. If seasonType = HalfYear, then seasonValue must be 1-2. 
+    <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. If seasonType = Half-year, then seasonValue must be 1-2. 
 Only a single value should be accepted in seasonValue</t>
   </si>
   <si>
-    <t>MM-DD</t>
+    <t>AreaType</t>
+  </si>
+  <si>
+    <t>ICESArea,  ICESAreaNonFAO</t>
+  </si>
+  <si>
+    <t>If needed the assessement input can be split by  ICES Area or fisheries management unit (ICESAreaNonFAO)</t>
+  </si>
+  <si>
+    <t>Conditional check: If AreaType = ICESArea, AreaValue uses from code type //vocab.ices.dk/?ref=358. If AreaType = ICESAreaNonFAO, AreaValue used from code type //vocab.ices.dk/?ref=1735
+Only a single value should be accepted in areaValue</t>
   </si>
 </sst>
 </file>
@@ -958,7 +897,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1019,9 +958,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1058,6 +994,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1400,7 +1342,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}">
+  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{D6F601CF-D10D-4B34-B869-DC6DC6EDCF02}" done="1">
     <text>//vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</text>
   </threadedComment>
   <threadedComment ref="J19" dT="2026-06-10T06:44:30.23" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{60AF2FFC-B021-42C7-AF40-A1560673A0CC}">
@@ -1411,7 +1353,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{56891298-F473-4CBE-ABBB-E1CEF089D4F3}">
+  <threadedComment ref="I12" dT="2026-04-30T08:28:50.08" personId="{4FF17731-8CB6-40F9-8A88-0C9953F00CDB}" id="{23CC9277-FDAF-43EE-8833-E4C0F8790F2B}" done="1">
     <text>//vocab.ices.dk/?ref=1446 doesn’t contain the option of AreaNonFAO</text>
   </threadedComment>
   <threadedComment ref="J26" dT="2026-06-10T06:36:31.15" personId="{9BB525CD-6748-42D0-A8F3-2D6A01F5B1CE}" id="{04664D76-2F7C-44B0-ACC2-110B494715CD}">
@@ -1449,464 +1391,464 @@
         <v>2</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="25"/>
+      <c r="F2" s="24"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="25"/>
+      <c r="F3" s="24"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="29"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="27"/>
-      <c r="C5" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="29"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="27"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28" t="s">
+      <c r="D7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="27"/>
+      <c r="G7" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="26"/>
       <c r="I7" s="7"/>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27" t="s">
+      <c r="D8" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="30"/>
+      <c r="G8" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="29"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="30"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="29"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27" t="s">
+      <c r="D10" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="30"/>
+      <c r="G10" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="29"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27" t="s">
+      <c r="D11" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="30"/>
+      <c r="G11" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="29"/>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27" t="s">
+      <c r="D12" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="30"/>
+      <c r="G12" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="29"/>
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27" t="s">
+      <c r="D13" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="30"/>
+      <c r="G13" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="29"/>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27" t="s">
+      <c r="D14" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="30"/>
+      <c r="G14" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="29"/>
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="27"/>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27" t="s">
+      <c r="D15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="30"/>
+      <c r="G15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="29"/>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="27"/>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="26"/>
+      <c r="C16" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27" t="s">
+      <c r="D16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="30"/>
+      <c r="G16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="29"/>
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="27"/>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27" t="s">
+      <c r="D17" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="30"/>
+      <c r="G17" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="29"/>
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="27"/>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27" t="s">
+      <c r="D18" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="30"/>
+      <c r="G18" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="27"/>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27" t="s">
+      <c r="D19" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="27"/>
+      <c r="G19" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="26"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27" t="s">
+      <c r="D20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="27"/>
+      <c r="G20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="27"/>
-      <c r="C21" s="27" t="s">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27" t="s">
+      <c r="D21" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="27"/>
+      <c r="G21" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="27"/>
-      <c r="C22" s="27" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27" t="s">
+      <c r="D22" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="27"/>
+      <c r="G22" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="27"/>
-      <c r="C23" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27" t="s">
+      <c r="B23" s="26"/>
+      <c r="C23" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="27"/>
+      <c r="G23" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="26"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="27"/>
+      <c r="G24" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="26"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27" t="s">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="27"/>
+      <c r="G25" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="26"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="27"/>
+      <c r="G26" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="26"/>
       <c r="J26" s="3"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27"/>
+      <c r="G27" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="26"/>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="27" t="s">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="27"/>
+      <c r="G28" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="26"/>
       <c r="J28" s="3"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="27" t="s">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="32"/>
+      <c r="G29" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="31"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="27"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H31" s="27"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33" spans="4:8" x14ac:dyDescent="0.3">
       <c r="H33" s="5"/>
@@ -1974,7 +1916,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>26</v>
@@ -2032,7 +1974,7 @@
         <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="L3" s="15"/>
     </row>
@@ -2040,9 +1982,9 @@
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35" t="s">
-        <v>144</v>
+      <c r="B4" s="33"/>
+      <c r="C4" s="34" t="s">
+        <v>135</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>43</v>
@@ -2053,46 +1995,46 @@
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="40" t="s">
-        <v>146</v>
+      <c r="G4" s="39" t="s">
+        <v>137</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>147</v>
+      <c r="I4" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>138</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="34" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:13" s="33" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="34" t="s">
+      <c r="C5" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="L5" s="39"/>
+      <c r="E5" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2123,7 +2065,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2219,7 +2161,7 @@
         <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -2241,17 +2183,17 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>120</v>
+      <c r="G10" s="38" t="s">
+        <v>146</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>121</v>
+      <c r="I10" s="33" t="s">
+        <v>145</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -2282,11 +2224,11 @@
       <c r="I11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>154</v>
+      <c r="J11" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2308,17 +2250,17 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>141</v>
+      <c r="G12" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -2341,22 +2283,22 @@
         <v>44</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>48</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>139</v>
+        <v>113</v>
+      </c>
+      <c r="K13" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -2379,17 +2321,17 @@
         <v>44</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2409,16 +2351,16 @@
         <v>44</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="I15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="J15" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -2435,19 +2377,19 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="I16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="J16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="K16" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="17" spans="3:11" ht="388.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2455,19 +2397,19 @@
         <v>18</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="J17" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>78</v>
-      </c>
       <c r="K17" s="10" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
@@ -2475,21 +2417,21 @@
         <v>25</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="J18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="3:11" ht="72" x14ac:dyDescent="0.3">
       <c r="C19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>43</v>
@@ -2498,10 +2440,10 @@
         <v>4</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2540,7 +2482,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>26</v>
@@ -2558,7 +2500,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>32</v>
@@ -2588,24 +2530,24 @@
         <v>2</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35" t="s">
-        <v>144</v>
+      <c r="B4" s="33"/>
+      <c r="C4" s="34" t="s">
+        <v>135</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>43</v>
@@ -2616,46 +2558,46 @@
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="40" t="s">
-        <v>146</v>
+      <c r="G4" s="39" t="s">
+        <v>137</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>147</v>
+      <c r="I4" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>138</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="34" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+    <row r="5" spans="1:12" s="33" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="34" t="s">
+      <c r="C5" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="L5" s="39"/>
+      <c r="E5" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="L5" s="38"/>
     </row>
     <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2686,7 +2628,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -2804,17 +2746,17 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>120</v>
+      <c r="G10" s="38" t="s">
+        <v>146</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>121</v>
+      <c r="I10" s="33" t="s">
+        <v>145</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -2846,11 +2788,11 @@
       <c r="I11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>62</v>
+      <c r="J11" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="K11" s="38" t="s">
+        <v>148</v>
       </c>
       <c r="L11" s="10"/>
     </row>
@@ -2873,17 +2815,17 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>118</v>
+      <c r="G12" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
@@ -2906,22 +2848,22 @@
         <v>44</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>48</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>139</v>
+        <v>113</v>
+      </c>
+      <c r="K13" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -2944,17 +2886,17 @@
         <v>44</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L14" s="10"/>
     </row>
@@ -2975,16 +2917,16 @@
         <v>44</v>
       </c>
       <c r="G15" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="I15" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L15" s="10"/>
     </row>
@@ -3002,19 +2944,19 @@
         <v>44</v>
       </c>
       <c r="G16" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>72</v>
-      </c>
       <c r="I16" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>111</v>
-      </c>
       <c r="K16" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L16" s="10"/>
     </row>
@@ -3033,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L17" s="10"/>
       <c r="M17" s="19"/>
@@ -3052,10 +2994,10 @@
         <v>4</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="19"/>
@@ -3079,19 +3021,19 @@
         <v>44</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="I19" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="K19" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="L19" s="10"/>
     </row>
@@ -3112,19 +3054,19 @@
         <v>44</v>
       </c>
       <c r="G20" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="I20" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="J20" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="K20" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="L20" s="10"/>
     </row>
@@ -3145,19 +3087,19 @@
         <v>44</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="I21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="K21" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="L21" s="10"/>
     </row>
@@ -3175,19 +3117,19 @@
         <v>44</v>
       </c>
       <c r="G22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="I22" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>99</v>
-      </c>
       <c r="K22" s="10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -3205,19 +3147,19 @@
         <v>44</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="I23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="J23" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="K23" s="10" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L23" s="10"/>
     </row>
@@ -3226,14 +3168,14 @@
         <v>24</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G24" s="19"/>
       <c r="J24" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L24" s="10"/>
     </row>
@@ -3242,50 +3184,50 @@
         <v>25</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="10"/>
       <c r="J25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="C26" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L26" s="10"/>
     </row>
     <row r="27" spans="1:15" ht="72" x14ac:dyDescent="0.3">
       <c r="C27" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="33" t="s">
+      <c r="E27" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J27" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L27" s="10"/>
     </row>
@@ -3313,18 +3255,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>112</v>
+      <c r="A2" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3347,7 +3289,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3374,10 +3316,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3386,21 +3328,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF5149A2F9434B4282E37FA76C9DDAE3" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9daeb8933c56b40f3271bb867fbbc8d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a657112-7d30-43e0-84e9-071e428c6b63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d201b2d4740b92ddb00486e196a42d19" ns2:_="">
     <xsd:import namespace="9a657112-7d30-43e0-84e9-071e428c6b63"/>
@@ -3544,31 +3471,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA6BFD8-8F41-452A-AD77-0631547D8597}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3586,6 +3504,30 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" enabled="0" method="" siteId="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" removed="1"/>

--- a/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
+++ b/WGRDBESstockCoord/format/SCF/SCF_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/kibi_dtu_dk/Documents/RDBES_gits/RDBESstockCoord/WGRDBESstockCoord/format/SCF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\Rstudio\D1SCI\VISBIO\RDBESstockCoord\WGRDBESstockCoord\format\SCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="8_{831D6449-227D-4368-BDB5-713DB903B240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E6E2786-36F5-4AA6-91F2-5F53FA90FF38}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE5EF66-07D2-41E2-B974-B78990FCAE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
+    <workbookView xWindow="-38520" yWindow="-3105" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{455A1C5D-51B7-4FE3-BC96-D9B701AEC4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="SCF" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="151">
   <si>
     <t>Version</t>
   </si>
@@ -559,12 +559,6 @@
 Use 'mm' for the Length-related distribution types or WidthCarapace.</t>
   </si>
   <si>
-    <t>timeReferenceType</t>
-  </si>
-  <si>
-    <t>Depending on timeReferenceType this is either a calendar year or model year</t>
-  </si>
-  <si>
     <t>The value of the specified areaType.
 Only a single value is accepted</t>
   </si>
@@ -594,9 +588,6 @@
   </si>
   <si>
     <t xml:space="preserve">Combined Information (CI) </t>
-  </si>
-  <si>
-    <t>See comment in CC</t>
   </si>
   <si>
     <t>I think we need this, so you can report for both lan and dis or will this always be catch?</t>
@@ -649,10 +640,6 @@
     <t>FK to DC</t>
   </si>
   <si>
-    <t>The temporal aggregation period. Depending on timeReferenceType this is either a calendar time span or model time span.
-If needed the assessement input can be split by quarter,  month or half year</t>
-  </si>
-  <si>
     <t>SOP Calculation.
 For each CC combination (timeReferenceType, year, workingGroup, stock, catchCategory, seasonType, seasonValue, areaType, areaValue and fleetValue),  we first check if a CC exists with variableType = WeightLive. 
  If not, no SOP check is performed. 
@@ -673,26 +660,10 @@
     <t>YesNoFields</t>
   </si>
   <si>
-    <t>Indicate if year, seasonType and seasonValue align with a calendar year (Y) or follow a shifted cycle (model year) that spans across calendar years (N).
-For most stocks this will be Y. For a minority of stocks the time is shifted relative to a calendar during stock coordination, this can be indicated by setting calendar year to N</t>
-  </si>
-  <si>
     <t>yearStartDate</t>
   </si>
   <si>
     <t>M/O</t>
-  </si>
-  <si>
-    <t>If the year is shifted relative to a calendar during stock coordination, calendarYear = N, the indicate when the year start with month and day, MM-DD, e.g., 07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mandatory if calendarYear = N
-yearStartDate should equal for all rows associated with a stock
-</t>
-  </si>
-  <si>
-    <t>Mandatory if calendarYear = N
-yearStartDate should equal for all rows associated with a stock</t>
   </si>
   <si>
     <t>MM-DD</t>
@@ -711,21 +682,47 @@
 Only a single value is accepted</t>
   </si>
   <si>
-    <t>Conditional check: If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646. If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645. If seasonType = Half-year, then seasonValue must be 1-2. 
+    <t>AreaType</t>
+  </si>
+  <si>
+    <t>ICESArea,  ICESAreaNonFAO</t>
+  </si>
+  <si>
+    <t>If needed the assessement input can be split by  ICES Area or fisheries management unit (ICESAreaNonFAO)</t>
+  </si>
+  <si>
+    <t>Indicates whether year, seasonType, and seasonValue follow the calendar year (Y) or a shifted cycle/model year spanning multiple calendar years (N).
+For most stocks, this value is Y. Use N only when the stock's reporting cycle is offset from the calendar year.</t>
+  </si>
+  <si>
+    <t>When calendarYear = N, specifies the start date of the shifted reporting year in MM-DD format (e.g., 07-01).</t>
+  </si>
+  <si>
+    <t>Mandatory if calendarYear = N. Leave blank if calendarYear = Y.
+ yearStartDate must be the same for all rows associated with a stock.</t>
+  </si>
+  <si>
+    <t>Depending on calendarYear, this represents either a calendar year or a model year.</t>
+  </si>
+  <si>
+    <t>The temporal aggregation period. Depending on calendarYear, this represents either a calendar period or a model-year period.
+If needed the assessement input can be split by quarter,  month or half year</t>
+  </si>
+  <si>
+    <t>Conditional check: 
+If SeasonType = Month, SeasonValue uses from code type //vocab.ices.dk/?ref=1646.
+If SeasonType=Quarter, SeasonValue used from code type //vocab.ices.dk/?ref=1645.
+ If seasonType = Half-year, then seasonValue must be 1-2. 
 Only a single value should be accepted in seasonValue</t>
   </si>
   <si>
-    <t>AreaType</t>
-  </si>
-  <si>
-    <t>ICESArea,  ICESAreaNonFAO</t>
-  </si>
-  <si>
-    <t>If needed the assessement input can be split by  ICES Area or fisheries management unit (ICESAreaNonFAO)</t>
-  </si>
-  <si>
-    <t>Conditional check: If AreaType = ICESArea, AreaValue uses from code type //vocab.ices.dk/?ref=358. If AreaType = ICESAreaNonFAO, AreaValue used from code type //vocab.ices.dk/?ref=1735
+    <t>Conditional check:
+If AreaType = ICESArea, AreaValue uses from code type //vocab.ices.dk/?ref=358.
+If AreaType = ICESAreaNonFAO, AreaValue used from code type //vocab.ices.dk/?ref=1735
 Only a single value should be accepted in areaValue</t>
+  </si>
+  <si>
+    <t>Only a single value is accepted here. If a combination of ICES areas are used as a single unit in the model, then this combination needs to be added as fisheries management unit in the AreaNonFAO code list</t>
   </si>
 </sst>
 </file>
@@ -843,7 +840,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -859,12 +856,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -897,7 +888,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -959,9 +950,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -977,27 +965,24 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1368,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:O84"/>
+  <dimension ref="B1:O85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="27.44140625" customWidth="1"/>
@@ -1402,482 +1387,500 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="28"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="27"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="26"/>
-      <c r="C5" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="28"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="26"/>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27" t="s">
+      <c r="D7" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="26"/>
+      <c r="G7" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="25"/>
       <c r="I7" s="7"/>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="26"/>
-      <c r="C8" s="26" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26" t="s">
+      <c r="D8" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="29"/>
+      <c r="G8" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="28"/>
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="26"/>
-      <c r="C9" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="29"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="28"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="26"/>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="28"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26" t="s">
+      <c r="D11" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="29"/>
-      <c r="N10" s="5"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="26"/>
-      <c r="C11" s="26" t="s">
+      <c r="G11" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="28"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26" t="s">
+      <c r="D12" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="29"/>
-      <c r="N11" s="5"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="26"/>
-      <c r="C12" s="26" t="s">
+      <c r="G12" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26" t="s">
+      <c r="D13" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="29"/>
-      <c r="N12" s="5"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="26"/>
-      <c r="C13" s="26" t="s">
+      <c r="G13" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+      <c r="D14" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="29"/>
-      <c r="N13" s="5"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="26"/>
-      <c r="C14" s="26" t="s">
+      <c r="G14" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26" t="s">
+      <c r="D15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="29"/>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="26"/>
-      <c r="C15" s="26" t="s">
+      <c r="G15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="28"/>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B16" s="25"/>
+      <c r="C16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26" t="s">
+      <c r="D16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="29"/>
-      <c r="N15" s="5"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="26"/>
-      <c r="C16" s="26" t="s">
+      <c r="G16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="25"/>
+      <c r="C17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26" t="s">
+      <c r="D17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="29"/>
-      <c r="N16" s="5"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="26"/>
-      <c r="C17" s="26" t="s">
+      <c r="G17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26" t="s">
+      <c r="D18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="29"/>
-      <c r="N17" s="5"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="26"/>
-      <c r="C18" s="26" t="s">
+      <c r="G18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="28"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26" t="s">
+      <c r="D19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26" t="s">
+      <c r="G19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="28"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26" t="s">
+      <c r="D20" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="26"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="26"/>
-      <c r="C20" s="26" t="s">
+      <c r="G20" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="25"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26" t="s">
+      <c r="D21" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="26"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="26"/>
-      <c r="C21" s="26" t="s">
+      <c r="G21" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="25"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="25"/>
+      <c r="C22" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26" t="s">
+      <c r="D22" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="26"/>
-      <c r="C22" s="26" t="s">
+      <c r="G22" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="25"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="25"/>
+      <c r="C23" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26" t="s">
+      <c r="D23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="26"/>
-      <c r="C23" s="30" t="s">
+      <c r="G23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="25"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="25"/>
+      <c r="C24" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26" t="s">
+      <c r="D24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26" t="s">
+      <c r="G24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="25"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="26"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26" t="s">
+      <c r="G25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="25"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26" t="s">
+      <c r="G26" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="25"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26" t="s">
+      <c r="G27" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="26" t="s">
+      <c r="G28" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="25"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="26" t="s">
+      <c r="G29" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="25"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="31"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="26" t="s">
+      <c r="G30" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="30"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="G30" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="26"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="30" t="s">
+      <c r="G31" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="H31" s="26"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="G32" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="25"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H34" s="5"/>
     </row>
-    <row r="46" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-    </row>
-    <row r="48" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-    </row>
-    <row r="80" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J80" s="3"/>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H35" s="5"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
     </row>
     <row r="81" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J81" s="3"/>
     </row>
     <row r="82" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J82" s="5"/>
+      <c r="J82" s="3"/>
     </row>
     <row r="83" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J83" s="5"/>
     </row>
     <row r="84" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J85" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1916,7 +1919,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>26</v>
@@ -1974,67 +1977,67 @@
         <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:13" ht="106.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:13" s="32" customFormat="1" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="32" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="38" t="s">
+      <c r="F5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="33" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="L5" s="38"/>
+      <c r="K5" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2065,7 +2068,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -2161,7 +2164,7 @@
         <v>57</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -2183,17 +2186,17 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>145</v>
+      <c r="I10" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -2224,10 +2227,10 @@
       <c r="I11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="K11" s="38" t="s">
+      <c r="J11" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" s="34" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2250,20 +2253,20 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="H12" s="41" t="s">
+      <c r="G12" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I12" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
@@ -2292,13 +2295,13 @@
         <v>48</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>152</v>
+        <v>111</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>149</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -2328,7 +2331,7 @@
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>65</v>
@@ -2409,7 +2412,7 @@
         <v>77</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.3">
@@ -2443,7 +2446,7 @@
         <v>80</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2462,13 +2465,14 @@
     <col min="2" max="2" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="9" customWidth="1"/>
     <col min="6" max="6" width="26" style="10" customWidth="1"/>
     <col min="7" max="7" width="38.88671875" style="9" customWidth="1"/>
-    <col min="8" max="9" width="27.44140625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="34.44140625" style="9" customWidth="1"/>
     <col min="10" max="10" width="78.109375" style="10" customWidth="1"/>
     <col min="11" max="11" width="106.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="64.33203125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="98" style="9" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
@@ -2538,66 +2542,66 @@
         <v>83</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="32" customFormat="1" ht="106.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="32" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="38" t="s">
+      <c r="F5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="33" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="L5" s="38"/>
+      <c r="K5" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="34"/>
     </row>
     <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -2628,7 +2632,7 @@
         <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -2746,17 +2750,17 @@
       <c r="F10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>145</v>
+      <c r="I10" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="L10" s="10"/>
     </row>
@@ -2788,10 +2792,10 @@
       <c r="I11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="K11" s="38" t="s">
+      <c r="J11" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" s="34" t="s">
         <v>148</v>
       </c>
       <c r="L11" s="10"/>
@@ -2815,20 +2819,20 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="H12" s="41" t="s">
+      <c r="G12" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="J12" s="38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I12" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
@@ -2857,13 +2861,13 @@
         <v>48</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="38" t="s">
-        <v>152</v>
+        <v>111</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>149</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
@@ -2893,7 +2897,7 @@
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>65</v>
@@ -2926,7 +2930,7 @@
         <v>108</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L15" s="10"/>
     </row>
@@ -2956,7 +2960,7 @@
         <v>110</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L16" s="10"/>
     </row>
@@ -2997,7 +3001,7 @@
         <v>85</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="19"/>
@@ -3129,7 +3133,7 @@
         <v>98</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L22" s="10"/>
     </row>
@@ -3159,7 +3163,7 @@
         <v>102</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L23" s="10"/>
     </row>
@@ -3202,14 +3206,14 @@
       <c r="D26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>80</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L26" s="10"/>
     </row>
@@ -3220,7 +3224,7 @@
       <c r="D27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="9" t="s">
@@ -3250,46 +3254,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0D8D43-BD49-469F-B11E-5FFF6EA58D41}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>121</v>
+      <c r="A2" s="8" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="s">
-        <v>122</v>
+      <c r="D5" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3316,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3472,18 +3471,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3505,6 +3504,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEB43D0-560F-48CD-B064-47F998E79E6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="9a657112-7d30-43e0-84e9-071e428c6b63"/>
@@ -3520,14 +3527,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F724DB8-FDC9-4526-B07B-463F4D815618}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" enabled="0" method="" siteId="{e0b220ce-5735-4468-91df-05cae5ff1fdc}" removed="1"/>
